--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92181008</v>
+        <v>136497421</v>
       </c>
       <c r="B2" t="n">
-        <v>104628</v>
+        <v>108366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>220083</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,28 +713,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillsjön Färna, Vstm</t>
+          <t>fdSågen2, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548228</v>
+        <v>548124</v>
       </c>
       <c r="R2" t="n">
-        <v>6626780</v>
+        <v>6626523</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,12 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-04-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-04-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,24 +775,143 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Åravin</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tina Nordberg</t>
+          <t>Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tina Nordberg, Kenneth Nordberg</t>
+          <t>Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136497421</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>92181008</v>
+      </c>
+      <c r="B3" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lillsjön Färna, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>548228</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6626780</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-04-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-04-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Åravin</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tina Nordberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tina Nordberg, Kenneth Nordberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/92181008</t>
         </is>
@@ -805,6 +920,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136497421</v>
       </c>
       <c r="B2" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
